--- a/01-Projects/에이팜건강-주간자금계획-자동화/양식/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/양식/에이팜건강_자금계획_기준파일.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +31,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="13"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F1F1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -80,13 +91,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,59 +479,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>· 카드결제기준: 법인카드 결제일 계산 기준. 실제 카드 약정에 맞게</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  결제일과 이용기간을 반드시 수정해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  이용기간은 '전전월/전월/당월 N일' 또는 '… 말일' 형식으로 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>· 주간조정: 자금계획에 수동으로 반영할 입금/지출 조정액을 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  (예: 일회성 대출 상환, 투자금 입금 등)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>· 계좌목록: 회사 계좌 목록(참고용). 내부이체 판정 키워드는</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  00_프로그램/classify_rules.json에서 관리합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>· 이 파일은 04_기준파일 폴더에 두고 파일명을 바꾸지 않습니다.</t>
         </is>
@@ -548,107 +561,107 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>카드구분</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>카드사</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>결제일</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>이용기간 시작일</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>이용기간 종료일</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>출금계좌</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>사용여부</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>우리카드</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>우리카드</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>전월 1일</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>전월 말일</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>우리은행 법인계좌</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>국민카드</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>KB국민카드</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>전월 13일</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>당월 12일</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>국민은행 법인계좌</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
@@ -680,526 +693,526 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>조정입금</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>조정지출</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n"/>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n"/>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
+      <c r="A66" s="5" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
+      <c r="A70" s="5" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
+      <c r="A74" s="5" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n"/>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="5" t="n"/>
+      <c r="A78" s="5" t="n"/>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n"/>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
+      <c r="A81" s="5" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n"/>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
+      <c r="A82" s="5" t="n"/>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n"/>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n"/>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n"/>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="n"/>
+      <c r="A86" s="5" t="n"/>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
+      <c r="A89" s="5" t="n"/>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n"/>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="5" t="n"/>
-      <c r="C91" s="5" t="n"/>
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n"/>
-      <c r="B92" s="5" t="n"/>
-      <c r="C92" s="5" t="n"/>
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n"/>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n"/>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
+      <c r="A94" s="5" t="n"/>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n"/>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n"/>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
+      <c r="A97" s="5" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="5" t="n"/>
+      <c r="A98" s="5" t="n"/>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="5" t="n"/>
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="5" t="n"/>
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1212,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1221,55 +1234,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>계좌번호</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>농협</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>주거래</t>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>수금(소액)·콕송금</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>우리은행</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>세금·보험 출금</t>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>스마트스토어 정산·세금</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>국민은행</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>급여 이체</t>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>주거래·급여</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>국민은행</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>보험·네이버 정산용</t>
         </is>
       </c>
     </row>

--- a/01-Projects/에이팜건강-주간자금계획-자동화/양식/에이팜건강_자금계획_기준파일.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/양식/에이팜건강_자금계획_기준파일.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>우리카드</t>
+          <t>국민카드</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>우리카드</t>
+          <t>KB국민카드</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -613,17 +613,17 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>전월 1일</t>
+          <t>전월 2일</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>전월 말일</t>
+          <t>당월 1일</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>우리은행 법인계좌</t>
+          <t>국민은행 법인계좌</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -635,33 +635,68 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>국민카드</t>
+          <t>우리카드</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>KB국민카드</t>
+          <t>우리카드</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>전월 13일</t>
+          <t>전월 10일</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>당월 12일</t>
+          <t>당월 9일</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>국민은행 법인계좌</t>
+          <t>우리은행 법인계좌</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>농협카드</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>NH농협카드</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>전월 10일</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>당월 9일</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>농협 법인계좌</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
